--- a/005_品質マネジメント/テスト項目書_デシジョンテーブル.xlsx
+++ b/005_品質マネジメント/テスト項目書_デシジョンテーブル.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/project-management-toolbox/005_品質マネジメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651F187E-B485-274A-971A-220B4934AB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF71E50C-8420-C445-BC14-0C38096872AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37500" yWindow="2180" windowWidth="28300" windowHeight="16900" xr2:uid="{FB9F2275-D551-E54D-8C69-FD8C942F700D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{FB9F2275-D551-E54D-8C69-FD8C942F700D}"/>
   </bookViews>
   <sheets>
-    <sheet name="SUM" sheetId="2" r:id="rId1"/>
-    <sheet name="case1" sheetId="1" r:id="rId2"/>
+    <sheet name="テストケース一覧" sheetId="2" r:id="rId1"/>
+    <sheet name="1" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,15 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="36">
-  <si>
-    <t>レンタルビデオの料金割引のデシジョンテーブル</t>
-    <rPh sb="8" eb="12">
-      <t>リョウキンワ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
   <si>
     <t>条件</t>
     <rPh sb="0" eb="2">
@@ -135,13 +150,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>アクション・期待値</t>
-    <rPh sb="6" eb="9">
-      <t xml:space="preserve">キタイチ </t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>料金</t>
     <rPh sb="0" eb="2">
       <t xml:space="preserve">リョウキン </t>
@@ -168,14 +176,6 @@
     <rPh sb="0" eb="2">
       <t xml:space="preserve">タナカ </t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>case1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>case2</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -233,10 +233,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>シート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>テストケース名</t>
     <rPh sb="6" eb="7">
       <t xml:space="preserve">メイ </t>
@@ -274,6 +270,54 @@
     </rPh>
     <rPh sb="12" eb="15">
       <t xml:space="preserve">ワリビキリツ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>件数</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ケンスウ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待値</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">キタイチ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テスト名</t>
+    <rPh sb="3" eb="4">
+      <t xml:space="preserve">メイ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成者/承認者</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">サクセイ </t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t xml:space="preserve">シャ </t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t xml:space="preserve">ショウニンシャ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作成日</t>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">サクセイビ </t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">ビコウ </t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -283,9 +327,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="180" formatCode="m/d;@"/>
+    <numFmt numFmtId="176" formatCode="m/d;@"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -308,8 +352,15 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -346,8 +397,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -432,15 +489,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -462,7 +510,29 @@
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -475,7 +545,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -483,76 +553,88 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -871,97 +953,93 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="1"/>
+    <col min="1" max="1" width="5.85546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="10.7109375" style="1"/>
+    <col min="3" max="3" width="49.28515625" style="1" customWidth="1"/>
+    <col min="4" max="8" width="8.5703125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F1" s="5" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="B1" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
+      </c>
+      <c r="D2" s="2" cm="1">
+        <f t="array" aca="1" ref="D2" ca="1">INDIRECT($A2&amp;"!$D$4")</f>
+        <v>6</v>
       </c>
       <c r="E2" s="2">
-        <f>COUNTA(case1!$D$2:$AX$2)</f>
-        <v>6</v>
-      </c>
-      <c r="F2" s="2">
-        <f>SUM(G2:I2)</f>
-        <v>5</v>
-      </c>
-      <c r="G2" s="2">
-        <f>COUNTIF(case1!$D$11:$AX$11,"OK")</f>
+        <f ca="1">SUM(F2:H2)</f>
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" cm="1">
+        <f t="array" aca="1" ref="F2" ca="1">INDIRECT($A2&amp;"!$E$4")</f>
         <v>4</v>
       </c>
-      <c r="H2" s="2">
-        <f>COUNTIF(case1!$D$11:$AX$11,"NG")</f>
+      <c r="G2" s="2" cm="1">
+        <f t="array" aca="1" ref="G2" ca="1">INDIRECT($A2&amp;"!$F$4")</f>
         <v>1</v>
       </c>
-      <c r="I2" s="2">
-        <f>COUNTIF(case1!$D$11:$AX$11,"N/A")</f>
+      <c r="H2" s="2" cm="1">
+        <f t="array" aca="1" ref="H2" ca="1">INDIRECT($A2&amp;"!$G$4")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:8">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" fitToHeight="10" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="58" fitToHeight="10" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"游ゴシック Regular,標準"&amp;K000000&amp;F / &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"游ゴシック Regular,標準"&amp;K000000&amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -970,287 +1048,356 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="2" width="10.7109375" style="1"/>
-    <col min="3" max="3" width="20.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" style="1" customWidth="1"/>
     <col min="4" max="9" width="4.28515625" style="1" customWidth="1"/>
     <col min="10" max="16384" width="10.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="str">
+        <f>テストケース一覧!B2</f>
+        <v>レンタルビデオの料金割引</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>テストケース一覧!C2</f>
+        <v>新旧作・年齢条件に応じた割引率</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2">
+        <f>COUNTA(6:6)</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="2">
+        <f>COUNTIF(15:15,"OK")</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <f>COUNTIF(15:15,"NG")</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <f>COUNTIF(15:15,"N/A")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="D2" s="9">
+    <row r="6" spans="1:9">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E6" s="6">
         <v>2</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F6" s="6">
         <v>3</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G6" s="6">
         <v>4</v>
       </c>
-      <c r="H2" s="9">
-        <v>5</v>
-      </c>
-      <c r="I2" s="9">
+      <c r="H6" s="6">
+        <v>5</v>
+      </c>
+      <c r="I6" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
+    <row r="7" spans="1:9">
+      <c r="A7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="16"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="16"/>
+      <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="15" t="s">
+      <c r="C9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="17"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="15"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="8"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="10" t="s">
+      <c r="D11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="18"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="18"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="18"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" ht="31" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="10"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="10"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="10"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:9" ht="31" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="E15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="I15" s="26"/>
+    </row>
+    <row r="16" spans="1:9" ht="31" customHeight="1">
+      <c r="A16" s="13"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="25"/>
+    </row>
+    <row r="17" spans="1:9" ht="43" customHeight="1">
+      <c r="A17" s="13"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="27">
+        <v>45699</v>
+      </c>
+      <c r="E17" s="28">
+        <v>45699</v>
+      </c>
+      <c r="F17" s="28">
+        <v>45699</v>
+      </c>
+      <c r="G17" s="28">
+        <v>45699</v>
+      </c>
+      <c r="H17" s="28">
+        <v>45700</v>
+      </c>
+      <c r="I17" s="28"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="13"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" spans="1:9" ht="31" customHeight="1">
-      <c r="A12" s="22"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" spans="1:9" ht="43" customHeight="1">
-      <c r="A13" s="22"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="18">
-        <v>45699</v>
-      </c>
-      <c r="E13" s="17">
-        <v>45699</v>
-      </c>
-      <c r="F13" s="17">
-        <v>45699</v>
-      </c>
-      <c r="G13" s="17">
-        <v>45699</v>
-      </c>
-      <c r="H13" s="17">
-        <v>45700</v>
-      </c>
-      <c r="I13" s="17"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="2"/>
+      <c r="E18" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="26"/>
+    </row>
+    <row r="19" spans="1:9" ht="142" customHeight="1">
+      <c r="A19" s="14"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A11:A14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="10" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="8" fitToHeight="20" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"游ゴシック Regular,標準"&amp;K000000&amp;F / &amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"游ゴシック Regular,標準"&amp;K000000&amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>